--- a/Migration_NZ.xlsx
+++ b/Migration_NZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Documents\DATA309\Datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/264e78913d06a81a/Desktop/Data science/data309/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{164F3992-F203-436B-9336-C7B2AF60CBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{164F3992-F203-436B-9336-C7B2AF60CBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B032AEAB-3996-48B6-88B7-DD19DE7628DF}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="16920" windowHeight="10450" xr2:uid="{DF9F759A-A88F-439F-8FFD-4D3D6227F4C4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DF9F759A-A88F-439F-8FFD-4D3D6227F4C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -425,6 +425,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2C40D1-44C2-442A-9CC4-C983ACF9AE5E}">
   <dimension ref="A1:D291"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -4502,5 +4508,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>